--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C795C1-E01F-48BC-BF51-A303A0BBB049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3728C0C9-49AE-4DC2-AAEE-BD26567F9E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="constraint" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>pset_ci</t>
   </si>
@@ -33,73 +44,52 @@
     <t>EST</t>
   </si>
   <si>
-    <t>~TFM_INS-TS</t>
-  </si>
-  <si>
-    <t>attribute</t>
-  </si>
-  <si>
-    <t>pset_set</t>
-  </si>
-  <si>
-    <t>process</t>
-  </si>
-  <si>
-    <t>attrib_cond</t>
-  </si>
-  <si>
-    <t>limtype</t>
-  </si>
-  <si>
-    <t>other_indexes</t>
-  </si>
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>rcap_bnd</t>
-  </si>
-  <si>
-    <t>ep_*</t>
-  </si>
-  <si>
-    <t>up</t>
-  </si>
-  <si>
-    <t>coal</t>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T:UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UC_max_oil_shale_capacity</t>
+  </si>
+  <si>
+    <t>Subcritical Coal,Supercritical Coal</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="186"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="186"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -117,7 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -125,39 +115,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -436,85 +402,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:M6"/>
+  <dimension ref="B5:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="2" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>2035</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2022</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2035</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="K6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3728C0C9-49AE-4DC2-AAEE-BD26567F9E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE2CBD8-AD01-465E-B310-6D8C72B6540C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,67 +36,55 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>EST</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
   <si>
-    <t>~UC_T:UC_RHSRT</t>
-  </si>
-  <si>
     <t>UC_N</t>
   </si>
   <si>
     <t>Pset_Set</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
     <t>UC_CAP</t>
   </si>
   <si>
     <t>UC_RHSRT~0</t>
   </si>
   <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
     <t>UC_max_oil_shale_capacity</t>
   </si>
   <si>
     <t>Subcritical Coal,Supercritical Coal</t>
   </si>
   <si>
-    <t>UP</t>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>UC_ACT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>~UC_T:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,9 +107,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,77 +389,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:J9"/>
+  <dimension ref="B5:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>2</v>
       </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>2022</v>
+      </c>
+      <c r="I8">
+        <v>2035</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="s">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="F8" t="s">
+      <c r="C9" t="s">
         <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>2035</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>5</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE2CBD8-AD01-465E-B310-6D8C72B6540C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972F436B-C3B4-44CB-BF08-2154CE7B61E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
     <t>UC_RHSRT</t>
   </si>
   <si>
-    <t>~UC_T:</t>
+    <t>~UC_T:2035</t>
   </si>
 </sst>
 </file>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:K9"/>
+  <dimension ref="B5:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -399,20 +399,20 @@
     <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>2</v>
       </c>
@@ -434,17 +434,14 @@
       <c r="H8">
         <v>2022</v>
       </c>
-      <c r="I8">
-        <v>2035</v>
+      <c r="I8" t="s">
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -457,8 +454,8 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="K9">
-        <v>5</v>
+      <c r="J9">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972F436B-C3B4-44CB-BF08-2154CE7B61E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E4B99-ED8E-4809-9061-2D657E332DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
+    <t>~UC_T:UC_RHSRT</t>
   </si>
   <si>
     <t>UC_N</t>
@@ -50,6 +50,12 @@
     <t>Pset_Set</t>
   </si>
   <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
     <t>UC_CAP</t>
   </si>
   <si>
@@ -62,16 +68,16 @@
     <t>Subcritical Coal,Supercritical Coal</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>pset_co</t>
   </si>
   <si>
-    <t>UC_ACT</t>
-  </si>
-  <si>
     <t>UC_RHSRT</t>
   </si>
   <si>
-    <t>~UC_T:2035</t>
+    <t>~UC_Sets: R_E: EST</t>
   </si>
 </sst>
 </file>
@@ -404,12 +410,12 @@
   <sheetData>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>11</v>
+      <c r="F7" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -423,39 +429,45 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
         <v>4</v>
       </c>
-      <c r="H8">
-        <v>2022</v>
-      </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
+      <c r="H9">
+        <v>2035</v>
+      </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E4B99-ED8E-4809-9061-2D657E332DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B597F-8084-4D6F-90FD-C93DDF0B954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>~UC_T:UC_RHSRT</t>
+    <t>~TFM_INS-TS</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>attrib_cond</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>rcap_bnd</t>
+  </si>
+  <si>
+    <t>up</t>
   </si>
   <si>
     <t>UC_N</t>
@@ -77,19 +104,40 @@
     <t>UC_RHSRT</t>
   </si>
   <si>
-    <t>~UC_Sets: R_E: EST</t>
+    <t>UC_Sets: R_E: EST</t>
+  </si>
+  <si>
+    <t>UC_T:UC_RHSRT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -101,7 +149,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,14 +157,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -395,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:J9"/>
+  <dimension ref="B1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -408,54 +480,111 @@
     <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2035</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>1</v>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B597F-8084-4D6F-90FD-C93DDF0B954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A45295-DB89-4827-B3F7-699E404D840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,39 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>~TFM_INS-TS</t>
-  </si>
-  <si>
-    <t>attribute</t>
-  </si>
-  <si>
-    <t>pset_set</t>
-  </si>
-  <si>
-    <t>process</t>
-  </si>
-  <si>
-    <t>attrib_cond</t>
-  </si>
-  <si>
-    <t>limtype</t>
-  </si>
-  <si>
-    <t>other_indexes</t>
-  </si>
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>rcap_bnd</t>
-  </si>
-  <si>
-    <t>up</t>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T:UC_RHSRT</t>
   </si>
   <si>
     <t>UC_N</t>
@@ -89,6 +68,9 @@
     <t>UC_RHSRT~0</t>
   </si>
   <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
     <t>UC_max_oil_shale_capacity</t>
   </si>
   <si>
@@ -96,25 +78,13 @@
   </si>
   <si>
     <t>UP</t>
-  </si>
-  <si>
-    <t>pset_co</t>
-  </si>
-  <si>
-    <t>UC_RHSRT</t>
-  </si>
-  <si>
-    <t>UC_Sets: R_E: EST</t>
-  </si>
-  <si>
-    <t>UC_T:UC_RHSRT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +109,12 @@
       <family val="2"/>
       <charset val="186"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,10 +157,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -467,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L9"/>
+  <dimension ref="B1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -480,124 +458,130 @@
     <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:14" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>2035</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>2022</v>
-      </c>
-      <c r="I2" s="2">
-        <v>2035</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
       <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
         <v>13</v>
       </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>2035</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="H8">
         <v>5</v>
       </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A45295-DB89-4827-B3F7-699E404D840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F650C5CF-AC97-433E-8E23-C743EDBB47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>pset_ci</t>
   </si>
@@ -44,6 +44,9 @@
     <t>EST</t>
   </si>
   <si>
+    <t>coal</t>
+  </si>
+  <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
   <si>
@@ -74,10 +77,10 @@
     <t>UC_max_oil_shale_capacity</t>
   </si>
   <si>
-    <t>Subcritical Coal,Supercritical Coal</t>
-  </si>
-  <si>
     <t>UP</t>
+  </si>
+  <si>
+    <t>ele</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -505,7 +508,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -514,31 +517,31 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -547,10 +550,13 @@
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
       </c>
       <c r="E7">
         <v>2035</v>
@@ -569,7 +575,10 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F650C5CF-AC97-433E-8E23-C743EDBB47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABC3C7-A0E1-4E56-8538-4C050BD5A47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>EST</t>
-  </si>
-  <si>
     <t>coal</t>
   </si>
   <si>
@@ -56,38 +53,26 @@
     <t>UC_N</t>
   </si>
   <si>
-    <t>Pset_Set</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
     <t>UC_CAP</t>
   </si>
   <si>
     <t>UC_RHSRT~0</t>
   </si>
   <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
-    <t>UC_max_oil_shale_capacity</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>ele</t>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>UC_ACT</t>
+  </si>
+  <si>
+    <t>UCE_max coal fleet utilization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,12 +97,6 @@
       <family val="2"/>
       <charset val="186"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,12 +139,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -462,135 +442,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6">
+        <v>2022</v>
+      </c>
+      <c r="H6">
+        <v>2035</v>
+      </c>
+      <c r="I6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2035</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
         <v>0</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABC3C7-A0E1-4E56-8538-4C050BD5A47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D425B3B2-48EE-4E57-8850-6FE87698C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -431,7 +431,7 @@
   <dimension ref="B1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
@@ -534,6 +534,9 @@
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
+      <c r="F7">
+        <v>1</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <v>0</v>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D425B3B2-48EE-4E57-8850-6FE87698C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F5E007-0D1A-404F-9BA8-5B09AAE2DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,36 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
-  </si>
-  <si>
-    <t>~UC_T:UC_RHSRT</t>
-  </si>
-  <si>
-    <t>UC_N</t>
-  </si>
-  <si>
-    <t>UC_CAP</t>
-  </si>
-  <si>
-    <t>UC_RHSRT~0</t>
-  </si>
-  <si>
-    <t>pset_co</t>
-  </si>
-  <si>
-    <t>UC_ACT</t>
-  </si>
-  <si>
-    <t>UCE_max coal fleet utilization</t>
+    <t>~TFM_INS-TS</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>attrib_cond</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>Supercritical Coal,Subcritical Coal</t>
   </si>
 </sst>
 </file>
@@ -139,8 +145,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
@@ -428,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N8"/>
+  <dimension ref="B1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -437,119 +445,115 @@
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="1" spans="2:13" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2035</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2022</v>
-      </c>
-      <c r="H6">
-        <v>2035</v>
-      </c>
-      <c r="I6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="I5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F5E007-0D1A-404F-9BA8-5B09AAE2DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF8EB1F-3D8D-4567-9C8D-673027BDBFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>pset_ci</t>
   </si>
   <si>
-    <t>~TFM_INS-TS</t>
-  </si>
-  <si>
     <t>attribute</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>Supercritical Coal,Subcritical Coal</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
   </si>
 </sst>
 </file>
@@ -478,26 +478,26 @@
     </row>
     <row r="3" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
     <row r="4" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -506,23 +506,23 @@
         <v>2035</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF8EB1F-3D8D-4567-9C8D-673027BDBFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4193F021-FAF6-4175-AEBC-36139C30440E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,6 +41,9 @@
     <t>pset_ci</t>
   </si>
   <si>
+    <t>~TFM_INS-TS</t>
+  </si>
+  <si>
     <t>attribute</t>
   </si>
   <si>
@@ -69,9 +72,6 @@
   </si>
   <si>
     <t>Supercritical Coal,Subcritical Coal</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
   </si>
 </sst>
 </file>
@@ -478,26 +478,26 @@
     </row>
     <row r="3" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
     <row r="4" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -506,23 +506,23 @@
         <v>2035</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4193F021-FAF6-4175-AEBC-36139C30440E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F650375E-B8B1-407C-856C-0593ED09EEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>pset_ci</t>
   </si>
   <si>
-    <t>~TFM_INS-TS</t>
-  </si>
-  <si>
     <t>attribute</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>Supercritical Coal,Subcritical Coal</t>
+  </si>
+  <si>
+    <t>TFM_INS-TS</t>
   </si>
 </sst>
 </file>
@@ -145,12 +145,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -436,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M8"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -448,56 +447,41 @@
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -506,23 +490,21 @@
         <v>2035</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -531,29 +513,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F650375E-B8B1-407C-856C-0593ED09EEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3E3F95-A105-4007-8FCE-91060A24FAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,49 +36,55 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>pset_ci</t>
   </si>
   <si>
-    <t>attribute</t>
-  </si>
-  <si>
-    <t>pset_set</t>
-  </si>
-  <si>
-    <t>process</t>
-  </si>
-  <si>
-    <t>attrib_cond</t>
-  </si>
-  <si>
-    <t>limtype</t>
-  </si>
-  <si>
-    <t>other_indexes</t>
-  </si>
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>up</t>
-  </si>
-  <si>
-    <t>cap_bnd</t>
-  </si>
-  <si>
-    <t>Supercritical Coal,Subcritical Coal</t>
-  </si>
-  <si>
-    <t>TFM_INS-TS</t>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T:UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UC_max_oil_shale_capacity</t>
+  </si>
+  <si>
+    <t>Subcritical Coal,Supercritical Coal</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +109,12 @@
       <family val="2"/>
       <charset val="186"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,14 +157,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -435,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:K7"/>
+  <dimension ref="B1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -448,78 +458,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="3"/>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>2035</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>2050</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2035</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="K9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_no_oil_shale_2035.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3E3F95-A105-4007-8FCE-91060A24FAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D5CA78-ADA3-4969-AF75-F0AEB8BA45C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,16 +116,66 @@
       <family val="2"/>
       <charset val="186"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -151,26 +201,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{9404145B-9CB8-474C-81A4-437CFD1BC573}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -445,9 +526,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:K9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -457,10 +539,13 @@
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -472,52 +557,44 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="I6" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -536,9 +613,8 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -554,9 +630,8 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>12</v>
       </c>
@@ -569,7 +644,6 @@
       <c r="H9">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
